--- a/Evidence_Checklist.xlsx
+++ b/Evidence_Checklist.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="163">
   <si>
     <t xml:space="preserve">Evidence ID</t>
   </si>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">A.5.15; A.8.3</t>
   </si>
   <si>
-    <t xml:space="preserve">Approved role-permission matrix and sampled access-denial test report</t>
+    <t xml:space="preserve">Approved GreenLeaf Role Matrix (Appendix A), documenting user roles, permitted actions, restricted access, and approval authorities.</t>
   </si>
   <si>
     <t xml:space="preserve">Lead Developer</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">A.5.18</t>
   </si>
   <si>
-    <t xml:space="preserve">Dated quarterly privileged and semiannual standard access-review sign-off sheets</t>
+    <t xml:space="preserve">A.5.15; A.5.18</t>
   </si>
   <si>
     <t xml:space="preserve">EV-007</t>
@@ -242,7 +242,10 @@
     <t xml:space="preserve">A.8.15; A.8.16</t>
   </si>
   <si>
-    <t xml:space="preserve">Dated authentication and access-change log export with reviewer sign-off</t>
+    <t xml:space="preserve">Approved change-control ticket for protected application routes or role permissions, including affected route, requested change, system-owner approval, authorization test results, deployment record, and dated access-change log with reviewer sign-off.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A.5.15; A.8.16; A.8.32</t>
   </si>
   <si>
     <t xml:space="preserve">EV-013</t>
@@ -521,6 +524,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -604,20 +608,24 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -998,1008 +1006,1008 @@
   <dimension ref="A1:K30"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="33.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="51.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="19.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="25.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="18.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="35.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="9.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="33.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="51.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="19.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="25.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="18.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="35.63"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="40" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2" t="s">
+      <c r="H3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2" t="s">
+      <c r="H4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2" t="s">
+      <c r="H5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2" t="s">
+      <c r="H6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="K7" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="H13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C14" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="D22" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="G13" s="2" t="s">
+      <c r="H26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G14" s="2" t="s">
+      <c r="H27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G15" s="2" t="s">
+      <c r="H28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="G16" s="2" t="s">
+      <c r="H29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F23" s="2" t="s">
+      <c r="H30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="G23" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="K29" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="66" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I30" s="2"/>
-      <c r="J30" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="K30" s="2" t="s">
+      <c r="K30" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2031,94 +2039,94 @@
   <dimension ref="A1:B11"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26.25"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="100"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26.25"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="100"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="32" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="B1" s="3"/>
+      <c r="A1" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>146</v>
       </c>
+      <c r="B2" s="3" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>148</v>
       </c>
+      <c r="B3" s="3" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>150</v>
       </c>
+      <c r="B4" s="3" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>152</v>
       </c>
+      <c r="B5" s="3" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="B6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>154</v>
       </c>
+      <c r="B6" s="3" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="A7" s="3" t="s">
         <v>156</v>
       </c>
+      <c r="B7" s="3" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B8" s="2" t="n">
+      <c r="A8" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B8" s="3" t="n">
         <v>29</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B9" s="2" t="n">
+      <c r="A9" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="B9" s="3" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="B10" s="2" t="n">
+      <c r="A10" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B10" s="3" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="A11" s="3" t="s">
         <v>161</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
